--- a/2025/FLORES DE ESTRADA/Julio/EDESUR Julio.xlsx
+++ b/2025/FLORES DE ESTRADA/Julio/EDESUR Julio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2025\FLORES DE ESTRADA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A51BD7F-EBF3-41FD-913F-10FD69074DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCE55D7-5DB6-4B42-8544-BB9E9736255A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataSignature="AMtx7miNZ3Aa6Oth2NTEJUZDCOk7UNfDow=="/>
     </ext>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
   <si>
     <t>EDESUR - VENCIMIENTO 6/11</t>
   </si>
@@ -235,18 +238,21 @@
   <si>
     <t>EDESUR - VENCIMIENTO 14/08</t>
   </si>
+  <si>
+    <t>SALDO DEUDOR:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="167" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,8 +339,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,6 +401,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -548,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -558,13 +578,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -572,62 +592,67 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -643,10 +668,6 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -971,21 +992,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1127,7 +1148,7 @@
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="59">
         <v>1547536.3</v>
       </c>
       <c r="E8" s="10"/>
@@ -1141,7 +1162,7 @@
       <c r="M8" s="12"/>
       <c r="N8" s="3"/>
       <c r="O8" s="2"/>
-      <c r="S8" s="44"/>
+      <c r="S8" s="43"/>
     </row>
     <row r="9" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -1162,13 +1183,13 @@
       <c r="F9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="34" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="34" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -1211,7 +1232,7 @@
       <c r="F10" s="18">
         <v>18790.099999999999</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="51">
         <v>19096.7</v>
       </c>
       <c r="H10" s="19">
@@ -1261,45 +1282,45 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="46">
         <v>2</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="46">
         <v>3.89</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="46">
         <v>17003.900000000001</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="56">
         <f>F11+70</f>
         <v>17073.900000000001</v>
       </c>
-      <c r="H11" s="48">
-        <v>0</v>
-      </c>
-      <c r="I11" s="49">
+      <c r="H11" s="47">
+        <v>0</v>
+      </c>
+      <c r="I11" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="49">
+      <c r="J11" s="48">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="50">
+      <c r="K11" s="49">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="48">
+      <c r="L11" s="47">
         <f>L9*E11/100</f>
         <v>46764.773159539996</v>
       </c>
-      <c r="M11" s="48">
+      <c r="M11" s="47">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
         <v>53330.373159539995</v>
       </c>
@@ -1322,51 +1343,51 @@
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
-      <c r="U11" s="33"/>
+      <c r="U11" s="32"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="40">
+      <c r="A12" s="39">
         <v>3</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="39">
         <v>3</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>4</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>11416.3</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="51">
         <f>F12+85</f>
         <v>11501.3</v>
       </c>
-      <c r="H12" s="41">
-        <v>0</v>
-      </c>
-      <c r="I12" s="42">
+      <c r="H12" s="40">
+        <v>0</v>
+      </c>
+      <c r="I12" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="41">
         <f t="shared" ref="J12:J33" si="5">(G12-F12)*93.78</f>
         <v>7971.3</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="42">
         <f>G12-F12</f>
         <v>85</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="40">
         <f>L9*E12/100</f>
         <v>48087.170343999991</v>
       </c>
-      <c r="M12" s="41">
+      <c r="M12" s="40">
         <f t="shared" si="3"/>
         <v>56059.470343999994</v>
       </c>
@@ -1387,44 +1408,44 @@
       <c r="A13" s="18">
         <v>4</v>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="39">
         <v>4</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="39">
         <v>4.9000000000000004</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="39">
         <v>28103</v>
       </c>
-      <c r="G13" s="52">
+      <c r="G13" s="51">
         <v>28598.880000000001</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="41">
         <f t="shared" si="5"/>
         <v>46503.626400000096</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="42">
         <f t="shared" si="2"/>
         <v>495.88000000000102</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="40">
         <f>L9*E13/100</f>
         <v>58906.7836714</v>
       </c>
-      <c r="M13" s="41">
+      <c r="M13" s="40">
         <f t="shared" si="3"/>
         <v>105411.4100714001</v>
       </c>
@@ -1445,44 +1466,44 @@
       <c r="A14" s="18">
         <v>5</v>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="39">
         <v>5</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="39">
         <v>3.89</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="39">
         <v>6130.2</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="51">
         <v>6426</v>
       </c>
       <c r="H14" s="26">
         <v>0</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="41">
         <f t="shared" si="5"/>
         <v>27740.124000000018</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="42">
         <f t="shared" si="2"/>
         <v>295.80000000000018</v>
       </c>
-      <c r="L14" s="41">
+      <c r="L14" s="40">
         <f>L9*E14/100</f>
         <v>46764.773159539996</v>
       </c>
-      <c r="M14" s="41">
+      <c r="M14" s="40">
         <f t="shared" si="3"/>
         <v>74505.897159540007</v>
       </c>
@@ -1502,65 +1523,65 @@
         <v>2540.8200000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:25" s="55" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40">
+    <row r="15" spans="1:25" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="39">
         <v>6</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="39">
         <v>6</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="39">
         <v>4</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="39">
         <v>13356.7</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="51">
         <f>F15+270</f>
         <v>13626.7</v>
       </c>
-      <c r="H15" s="41">
-        <v>0</v>
-      </c>
-      <c r="I15" s="42">
+      <c r="H15" s="40">
+        <v>0</v>
+      </c>
+      <c r="I15" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="41">
         <f t="shared" si="5"/>
         <v>25320.6</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="42">
         <f t="shared" si="2"/>
         <v>270</v>
       </c>
-      <c r="L15" s="41">
+      <c r="L15" s="40">
         <f>L9*E15/100</f>
         <v>48087.170343999991</v>
       </c>
-      <c r="M15" s="41">
+      <c r="M15" s="40">
         <f t="shared" si="3"/>
         <v>73408.77034399999</v>
       </c>
-      <c r="N15" s="53" t="e">
+      <c r="N15" s="52" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O15" s="54">
+      <c r="O15" s="53">
         <f>J15/L9*100</f>
         <v>2.1062249925595249</v>
       </c>
-      <c r="P15" s="42">
+      <c r="P15" s="41">
         <f>C7*O15/100</f>
         <v>1643.9086066927091</v>
       </c>
-      <c r="Y15" s="56"/>
+      <c r="Y15" s="55"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
@@ -1581,7 +1602,7 @@
       <c r="F16" s="18">
         <v>18568</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="51">
         <v>19037</v>
       </c>
       <c r="H16" s="19">
@@ -1639,7 +1660,7 @@
       <c r="F17" s="18">
         <v>6108.1</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="51">
         <v>6219.7</v>
       </c>
       <c r="H17" s="26">
@@ -1682,44 +1703,44 @@
       <c r="A18" s="18">
         <v>9</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="39">
         <v>9</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="39">
         <v>4</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="39">
         <v>20633.2</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="51">
         <v>21089</v>
       </c>
-      <c r="H18" s="46">
-        <v>0</v>
-      </c>
-      <c r="I18" s="42">
+      <c r="H18" s="45">
+        <v>0</v>
+      </c>
+      <c r="I18" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="41">
         <f t="shared" si="5"/>
         <v>42744.923999999934</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18" s="42">
         <f t="shared" si="2"/>
         <v>455.79999999999927</v>
       </c>
-      <c r="L18" s="41">
+      <c r="L18" s="40">
         <f>L9*E18/100</f>
         <v>48087.170343999991</v>
       </c>
-      <c r="M18" s="41">
+      <c r="M18" s="40">
         <f t="shared" si="3"/>
         <v>90833.094343999925</v>
       </c>
@@ -1740,44 +1761,44 @@
       <c r="A19" s="18">
         <v>10</v>
       </c>
-      <c r="B19" s="36">
+      <c r="B19" s="35">
         <v>10</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="35">
         <v>12.66</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="35">
         <v>23373.9</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="50">
         <v>23559</v>
       </c>
-      <c r="H19" s="37">
-        <v>0</v>
-      </c>
-      <c r="I19" s="38">
+      <c r="H19" s="36">
+        <v>0</v>
+      </c>
+      <c r="I19" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19" s="37">
         <f t="shared" si="5"/>
         <v>17358.677999999865</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="38">
         <f t="shared" si="2"/>
         <v>185.09999999999854</v>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="36">
         <f>L9*E19/100</f>
         <v>152195.89413875996</v>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="36">
         <f>J19+L19+1</f>
         <v>169555.57213875983</v>
       </c>
@@ -1795,48 +1816,48 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="40">
+      <c r="A20" s="39">
         <v>11</v>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="39">
         <v>11</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="39">
         <v>7.75</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="39">
         <v>17945.099999999999</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="51">
         <f>F20+200</f>
         <v>18145.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="41">
         <f t="shared" si="5"/>
         <v>18756</v>
       </c>
-      <c r="K20" s="43">
+      <c r="K20" s="42">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="L20" s="41">
+      <c r="L20" s="40">
         <f>L9*E20/100</f>
         <v>93168.892541499998</v>
       </c>
-      <c r="M20" s="41">
+      <c r="M20" s="40">
         <f t="shared" si="3"/>
         <v>111925.8925415</v>
       </c>
@@ -1854,47 +1875,47 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36">
+      <c r="A21" s="35">
         <v>12</v>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="35">
         <v>12</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="35">
         <v>7.51</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="35">
         <v>15067</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="50">
         <v>15144.8</v>
       </c>
-      <c r="H21" s="66">
-        <v>0</v>
-      </c>
-      <c r="I21" s="38">
+      <c r="H21" s="58">
+        <v>0</v>
+      </c>
+      <c r="I21" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21" s="37">
         <f t="shared" si="5"/>
         <v>7296.0839999999316</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="38">
         <f t="shared" si="2"/>
         <v>77.799999999999272</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="36">
         <f>L9*E21/100</f>
         <v>90283.662320859992</v>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="36">
         <f t="shared" si="3"/>
         <v>97580.746320859922</v>
       </c>
@@ -1916,48 +1937,48 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40">
+      <c r="A22" s="39">
         <v>13</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="35">
         <v>13</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="35">
         <v>4.45</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="35">
         <v>11028.2</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="50">
         <f>F22+193</f>
         <v>11221.2</v>
       </c>
-      <c r="H22" s="66">
-        <v>0</v>
-      </c>
-      <c r="I22" s="38">
+      <c r="H22" s="58">
+        <v>0</v>
+      </c>
+      <c r="I22" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="37">
         <f t="shared" si="5"/>
         <v>18099.54</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="38">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="36">
         <f>L9*E22/100</f>
         <v>53496.977007699992</v>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="36">
         <f t="shared" si="3"/>
         <v>71597.517007699993</v>
       </c>
@@ -1982,44 +2003,44 @@
       <c r="A23" s="18">
         <v>14</v>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="39">
         <v>14</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="39">
         <v>6.17</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="39">
         <v>20525.349999999999</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="51">
         <v>20525.400000000001</v>
       </c>
-      <c r="H23" s="41">
-        <v>0</v>
-      </c>
-      <c r="I23" s="42">
+      <c r="H23" s="40">
+        <v>0</v>
+      </c>
+      <c r="I23" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="41">
         <f t="shared" si="5"/>
         <v>4.6890000002729355</v>
       </c>
-      <c r="K23" s="43">
+      <c r="K23" s="42">
         <f t="shared" si="2"/>
         <v>5.0000000002910383E-2</v>
       </c>
-      <c r="L23" s="41">
+      <c r="L23" s="40">
         <f>L9*E23/100</f>
         <v>74174.460255619982</v>
       </c>
-      <c r="M23" s="41">
+      <c r="M23" s="40">
         <f>J23+L23+1</f>
         <v>74180.149255620257</v>
       </c>
@@ -2037,48 +2058,48 @@
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40">
+      <c r="A24" s="39">
         <v>15</v>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="39">
         <v>15</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="39">
         <v>4.45</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="39">
         <v>30484.400000000001</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="51">
         <f>F24+288</f>
         <v>30772.400000000001</v>
       </c>
-      <c r="H24" s="41">
-        <v>0</v>
-      </c>
-      <c r="I24" s="42">
+      <c r="H24" s="40">
+        <v>0</v>
+      </c>
+      <c r="I24" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="42">
+      <c r="J24" s="41">
         <f t="shared" si="5"/>
         <v>27008.639999999999</v>
       </c>
-      <c r="K24" s="43">
+      <c r="K24" s="42">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="L24" s="41">
+      <c r="L24" s="40">
         <f>L9*E24/100</f>
         <v>53496.977007699992</v>
       </c>
-      <c r="M24" s="41">
+      <c r="M24" s="40">
         <f t="shared" si="3"/>
         <v>80506.617007699999</v>
       </c>
@@ -2096,48 +2117,48 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="40">
+      <c r="A25" s="39">
         <v>16</v>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="39">
         <v>16</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="39">
         <v>9.19</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="39">
         <v>11470.8</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="51">
         <f>F25+179</f>
         <v>11649.8</v>
       </c>
-      <c r="H25" s="41">
-        <v>0</v>
-      </c>
-      <c r="I25" s="42">
+      <c r="H25" s="40">
+        <v>0</v>
+      </c>
+      <c r="I25" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="42">
+      <c r="J25" s="41">
         <f t="shared" si="5"/>
         <v>16786.62</v>
       </c>
-      <c r="K25" s="43">
+      <c r="K25" s="42">
         <f t="shared" si="2"/>
         <v>179</v>
       </c>
-      <c r="L25" s="41">
+      <c r="L25" s="40">
         <f>L9*E25/100</f>
         <v>110480.27386533999</v>
       </c>
-      <c r="M25" s="41">
+      <c r="M25" s="40">
         <f>J25+L25+1</f>
         <v>127267.89386533998</v>
       </c>
@@ -2155,44 +2176,44 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36">
+      <c r="A26" s="35">
         <v>17</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="39">
         <v>17</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="39">
         <v>1.18</v>
       </c>
-      <c r="F26" s="40">
-        <v>0</v>
-      </c>
-      <c r="G26" s="40">
-        <v>0</v>
-      </c>
-      <c r="H26" s="41">
-        <v>0</v>
-      </c>
-      <c r="I26" s="42">
+      <c r="F26" s="39">
+        <v>0</v>
+      </c>
+      <c r="G26" s="39">
+        <v>0</v>
+      </c>
+      <c r="H26" s="40">
+        <v>0</v>
+      </c>
+      <c r="I26" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="42">
+      <c r="J26" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41">
+      <c r="K26" s="40"/>
+      <c r="L26" s="40">
         <f>L9*E26/100</f>
         <v>14185.715251479996</v>
       </c>
-      <c r="M26" s="41">
+      <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
         <v>14185.715251479996</v>
       </c>
@@ -2213,41 +2234,41 @@
       <c r="A27" s="18">
         <v>18</v>
       </c>
-      <c r="B27" s="36">
+      <c r="B27" s="35">
         <v>18</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="35">
         <v>1.18</v>
       </c>
-      <c r="F27" s="36">
-        <v>0</v>
-      </c>
-      <c r="G27" s="36">
-        <v>0</v>
-      </c>
-      <c r="H27" s="37">
-        <v>0</v>
-      </c>
-      <c r="I27" s="38">
+      <c r="F27" s="35">
+        <v>0</v>
+      </c>
+      <c r="G27" s="35">
+        <v>0</v>
+      </c>
+      <c r="H27" s="36">
+        <v>0</v>
+      </c>
+      <c r="I27" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37">
+      <c r="K27" s="36"/>
+      <c r="L27" s="36">
         <f>L26</f>
         <v>14185.715251479996</v>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="36">
         <f t="shared" si="6"/>
         <v>14185.715251479996</v>
       </c>
@@ -2268,41 +2289,41 @@
       <c r="A28" s="18">
         <v>19</v>
       </c>
-      <c r="B28" s="36">
+      <c r="B28" s="35">
         <v>19</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="35">
         <v>1.18</v>
       </c>
-      <c r="F28" s="36">
-        <v>0</v>
-      </c>
-      <c r="G28" s="36">
-        <v>0</v>
-      </c>
-      <c r="H28" s="37">
-        <v>0</v>
-      </c>
-      <c r="I28" s="38">
+      <c r="F28" s="35">
+        <v>0</v>
+      </c>
+      <c r="G28" s="35">
+        <v>0</v>
+      </c>
+      <c r="H28" s="36">
+        <v>0</v>
+      </c>
+      <c r="I28" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37">
+      <c r="K28" s="36"/>
+      <c r="L28" s="36">
         <f>L27</f>
         <v>14185.715251479996</v>
       </c>
-      <c r="M28" s="37">
+      <c r="M28" s="36">
         <f t="shared" si="6"/>
         <v>14185.715251479996</v>
       </c>
@@ -2320,44 +2341,44 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="40">
+      <c r="A29" s="39">
         <v>20</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="39">
         <v>20</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="39">
         <v>1.18</v>
       </c>
-      <c r="F29" s="40">
-        <v>0</v>
-      </c>
-      <c r="G29" s="40">
-        <v>0</v>
-      </c>
-      <c r="H29" s="41">
-        <v>0</v>
-      </c>
-      <c r="I29" s="42">
+      <c r="F29" s="39">
+        <v>0</v>
+      </c>
+      <c r="G29" s="39">
+        <v>0</v>
+      </c>
+      <c r="H29" s="40">
+        <v>0</v>
+      </c>
+      <c r="I29" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="42">
+      <c r="J29" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41">
+      <c r="K29" s="40"/>
+      <c r="L29" s="40">
         <f>L28</f>
         <v>14185.715251479996</v>
       </c>
-      <c r="M29" s="41">
+      <c r="M29" s="40">
         <f t="shared" si="6"/>
         <v>14185.715251479996</v>
       </c>
@@ -2384,7 +2405,7 @@
       <c r="C30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="44" t="s">
         <v>63</v>
       </c>
       <c r="E30" s="18">
@@ -2485,44 +2506,44 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36">
+      <c r="A32" s="35">
         <v>23</v>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="39">
         <v>23</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="39">
         <v>1.18</v>
       </c>
-      <c r="F32" s="40">
-        <v>0</v>
-      </c>
-      <c r="G32" s="40">
-        <v>0</v>
-      </c>
-      <c r="H32" s="41">
-        <v>0</v>
-      </c>
-      <c r="I32" s="42">
+      <c r="F32" s="39">
+        <v>0</v>
+      </c>
+      <c r="G32" s="39">
+        <v>0</v>
+      </c>
+      <c r="H32" s="40">
+        <v>0</v>
+      </c>
+      <c r="I32" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="42">
+      <c r="J32" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41">
+      <c r="K32" s="40"/>
+      <c r="L32" s="40">
         <f t="shared" si="7"/>
         <v>14185.715251479996</v>
       </c>
-      <c r="M32" s="41">
+      <c r="M32" s="40">
         <f t="shared" si="6"/>
         <v>14185.715251479996</v>
       </c>
@@ -2540,44 +2561,44 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="40">
+      <c r="A33" s="39">
         <v>24</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="35">
         <v>24</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="65" t="s">
+      <c r="D33" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="35">
         <v>1.18</v>
       </c>
-      <c r="F33" s="36">
-        <v>0</v>
-      </c>
-      <c r="G33" s="36">
-        <v>0</v>
-      </c>
-      <c r="H33" s="37">
-        <v>0</v>
-      </c>
-      <c r="I33" s="38">
+      <c r="F33" s="35">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35">
+        <v>0</v>
+      </c>
+      <c r="H33" s="36">
+        <v>0</v>
+      </c>
+      <c r="I33" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="38">
+      <c r="J33" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37">
+      <c r="K33" s="36"/>
+      <c r="L33" s="36">
         <f t="shared" si="7"/>
         <v>14185.715251479996</v>
       </c>
-      <c r="M33" s="37">
+      <c r="M33" s="36">
         <f t="shared" si="6"/>
         <v>14185.715251479996</v>
       </c>
@@ -2635,116 +2656,129 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="61"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="66"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H36" s="5"/>
-      <c r="J36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="33"/>
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
+      <c r="M36" s="61">
+        <f>+M28+M27</f>
+        <v>28371.430502959993</v>
+      </c>
       <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H37" s="5"/>
-      <c r="K37" s="34">
+      <c r="K37" s="33">
         <f>J34+L34</f>
         <v>1547416.08207414</v>
       </c>
-      <c r="L37" s="34"/>
+      <c r="L37" s="33"/>
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="63"/>
-      <c r="K38" s="63"/>
-      <c r="L38" s="63"/>
-      <c r="M38" s="63"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="68"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="63"/>
-      <c r="K39" s="63"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="63"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="68"/>
+      <c r="M39" s="68"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="63"/>
-      <c r="K40" s="63"/>
-      <c r="L40" s="63"/>
-      <c r="M40" s="63"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="68"/>
+      <c r="M40" s="68"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="63"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="63"/>
-      <c r="K41" s="63"/>
-      <c r="L41" s="63"/>
-      <c r="M41" s="63"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="63"/>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="63"/>
-      <c r="M42" s="63"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="68"/>
+      <c r="J42" s="68"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="68"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6616,21 +6650,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8222,19 +8256,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="61"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="66"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
